--- a/test/fixtures/JinSheet-Styled-Sample.xlsx
+++ b/test/fixtures/JinSheet-Styled-Sample.xlsx
@@ -82,7 +82,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D10"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
